--- a/artfynd/A 18986-2024 artfynd.xlsx
+++ b/artfynd/A 18986-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118676090</v>
       </c>
       <c r="B2" t="n">
-        <v>78220</v>
+        <v>78227</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>118676089</v>
       </c>
       <c r="B3" t="n">
-        <v>78221</v>
+        <v>78228</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 18986-2024 artfynd.xlsx
+++ b/artfynd/A 18986-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118676090</v>
+        <v>118676089</v>
       </c>
       <c r="B2" t="n">
-        <v>78227</v>
+        <v>78228</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676089</v>
+        <v>118676090</v>
       </c>
       <c r="B3" t="n">
-        <v>78228</v>
+        <v>78227</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">

--- a/artfynd/A 18986-2024 artfynd.xlsx
+++ b/artfynd/A 18986-2024 artfynd.xlsx
@@ -1285,10 +1285,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134262331</v>
+        <v>134264254</v>
       </c>
       <c r="B8" t="n">
-        <v>79949</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1296,21 +1296,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520729</v>
+        <v>520475</v>
       </c>
       <c r="R8" t="n">
-        <v>6848525</v>
+        <v>6848386</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134264254</v>
+        <v>134262331</v>
       </c>
       <c r="B9" t="n">
-        <v>79359</v>
+        <v>79949</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1393,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520475</v>
+        <v>520729</v>
       </c>
       <c r="R9" t="n">
-        <v>6848386</v>
+        <v>6848525</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2066,10 +2066,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134263519</v>
+        <v>134263036</v>
       </c>
       <c r="B16" t="n">
-        <v>79117</v>
+        <v>79359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520595</v>
+        <v>520606</v>
       </c>
       <c r="R16" t="n">
-        <v>6848484</v>
+        <v>6848503</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134263036</v>
+        <v>134263519</v>
       </c>
       <c r="B17" t="n">
-        <v>79359</v>
+        <v>79117</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2174,21 +2174,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520606</v>
+        <v>520595</v>
       </c>
       <c r="R17" t="n">
-        <v>6848503</v>
+        <v>6848484</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2954,7 +2954,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134273485</v>
+        <v>134273492</v>
       </c>
       <c r="B25" t="n">
         <v>79359</v>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520469</v>
+        <v>520414</v>
       </c>
       <c r="R25" t="n">
-        <v>6848486</v>
+        <v>6848451</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3168,7 +3168,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134273492</v>
+        <v>134273485</v>
       </c>
       <c r="B27" t="n">
         <v>79359</v>
@@ -3203,10 +3203,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520414</v>
+        <v>520469</v>
       </c>
       <c r="R27" t="n">
-        <v>6848451</v>
+        <v>6848486</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3703,32 +3703,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134273452</v>
+        <v>134273496</v>
       </c>
       <c r="B32" t="n">
-        <v>79359</v>
+        <v>99181</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520856</v>
+        <v>520386</v>
       </c>
       <c r="R32" t="n">
-        <v>6848595</v>
+        <v>6848452</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3783,7 +3783,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>+100</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3810,32 +3815,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134273496</v>
+        <v>134273452</v>
       </c>
       <c r="B33" t="n">
-        <v>99181</v>
+        <v>79359</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3845,10 +3850,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520386</v>
+        <v>520856</v>
       </c>
       <c r="R33" t="n">
-        <v>6848452</v>
+        <v>6848595</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3880,7 +3885,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3890,12 +3895,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:12</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>+100</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 18986-2024 artfynd.xlsx
+++ b/artfynd/A 18986-2024 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>134263675</v>
       </c>
       <c r="B4" t="n">
-        <v>79383</v>
+        <v>79390</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>134264098</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>134262850</v>
       </c>
       <c r="B6" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>134263792</v>
       </c>
       <c r="B7" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>134264254</v>
       </c>
       <c r="B8" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>134262331</v>
       </c>
       <c r="B9" t="n">
-        <v>79949</v>
+        <v>79956</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>134263798</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>134262435</v>
       </c>
       <c r="B11" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>134262337</v>
       </c>
       <c r="B12" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>134263717</v>
       </c>
       <c r="B13" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>134262818</v>
       </c>
       <c r="B15" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2066,10 +2066,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134263036</v>
+        <v>134263810</v>
       </c>
       <c r="B16" t="n">
-        <v>79359</v>
+        <v>79124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2077,21 +2077,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520606</v>
+        <v>520420</v>
       </c>
       <c r="R16" t="n">
-        <v>6848503</v>
+        <v>6848482</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134263519</v>
+        <v>134263036</v>
       </c>
       <c r="B17" t="n">
-        <v>79117</v>
+        <v>79366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2174,21 +2174,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520595</v>
+        <v>520606</v>
       </c>
       <c r="R17" t="n">
-        <v>6848484</v>
+        <v>6848503</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2260,10 +2260,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134263810</v>
+        <v>134263519</v>
       </c>
       <c r="B18" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520420</v>
+        <v>520595</v>
       </c>
       <c r="R18" t="n">
-        <v>6848482</v>
+        <v>6848484</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
         <v>134262683</v>
       </c>
       <c r="B19" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>134263840</v>
       </c>
       <c r="B20" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>134262469</v>
       </c>
       <c r="B21" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>134262651</v>
       </c>
       <c r="B22" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>134263477</v>
       </c>
       <c r="B23" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>134273484</v>
       </c>
       <c r="B24" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2954,10 +2954,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134273492</v>
+        <v>134273463</v>
       </c>
       <c r="B25" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520414</v>
+        <v>520749</v>
       </c>
       <c r="R25" t="n">
-        <v>6848451</v>
+        <v>6848588</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3061,10 +3061,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134273463</v>
+        <v>134273485</v>
       </c>
       <c r="B26" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520749</v>
+        <v>520469</v>
       </c>
       <c r="R26" t="n">
-        <v>6848588</v>
+        <v>6848486</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3168,10 +3168,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134273485</v>
+        <v>134273492</v>
       </c>
       <c r="B27" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3203,10 +3203,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520469</v>
+        <v>520414</v>
       </c>
       <c r="R27" t="n">
-        <v>6848486</v>
+        <v>6848451</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3278,7 +3278,7 @@
         <v>134273437</v>
       </c>
       <c r="B28" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>134273464</v>
       </c>
       <c r="B29" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>134273462</v>
       </c>
       <c r="B30" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>134273461</v>
       </c>
       <c r="B31" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3703,32 +3703,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134273496</v>
+        <v>134273452</v>
       </c>
       <c r="B32" t="n">
-        <v>99181</v>
+        <v>79366</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520386</v>
+        <v>520856</v>
       </c>
       <c r="R32" t="n">
-        <v>6848452</v>
+        <v>6848595</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3783,12 +3783,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:12</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>+100</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3815,32 +3810,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134273452</v>
+        <v>134273496</v>
       </c>
       <c r="B33" t="n">
-        <v>79359</v>
+        <v>99188</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3850,10 +3845,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520856</v>
+        <v>520386</v>
       </c>
       <c r="R33" t="n">
-        <v>6848595</v>
+        <v>6848452</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3885,7 +3880,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3895,7 +3890,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>+100</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3922,10 +3922,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134273482</v>
+        <v>134273480</v>
       </c>
       <c r="B34" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3957,13 +3957,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520519</v>
+        <v>520593</v>
       </c>
       <c r="R34" t="n">
-        <v>6848489</v>
+        <v>6848428</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4029,10 +4029,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134273480</v>
+        <v>134273482</v>
       </c>
       <c r="B35" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520593</v>
+        <v>520519</v>
       </c>
       <c r="R35" t="n">
-        <v>6848428</v>
+        <v>6848489</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 18986-2024 artfynd.xlsx
+++ b/artfynd/A 18986-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118676090</v>
+        <v>134262435</v>
       </c>
       <c r="B2" t="n">
-        <v>78229</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillskog, Hls</t>
+          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520598</v>
+        <v>520749</v>
       </c>
       <c r="R2" t="n">
-        <v>6848474</v>
+        <v>6848568</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,66 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676089</v>
+        <v>134262683</v>
       </c>
       <c r="B3" t="n">
-        <v>78230</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillskog, Hls</t>
+          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520598</v>
+        <v>520808</v>
       </c>
       <c r="R3" t="n">
-        <v>6848474</v>
+        <v>6848642</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,17 +837,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,44 +862,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134263675</v>
+        <v>134262818</v>
       </c>
       <c r="B4" t="n">
-        <v>79390</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520443</v>
+        <v>520762</v>
       </c>
       <c r="R4" t="n">
-        <v>6848531</v>
+        <v>6848627</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,14 +971,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134264098</v>
+        <v>134263036</v>
       </c>
       <c r="B5" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1029,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520458</v>
+        <v>520606</v>
       </c>
       <c r="R5" t="n">
-        <v>6848420</v>
+        <v>6848503</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134262850</v>
+        <v>134263717</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1126,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520753</v>
+        <v>520420</v>
       </c>
       <c r="R6" t="n">
-        <v>6848624</v>
+        <v>6848523</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134263792</v>
+        <v>134263840</v>
       </c>
       <c r="B7" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1223,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520420</v>
+        <v>520423</v>
       </c>
       <c r="R7" t="n">
-        <v>6848482</v>
+        <v>6848466</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,14 +1262,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134264254</v>
+        <v>134264098</v>
       </c>
       <c r="B8" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1320,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520475</v>
+        <v>520458</v>
       </c>
       <c r="R8" t="n">
-        <v>6848386</v>
+        <v>6848420</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134262331</v>
+        <v>134264254</v>
       </c>
       <c r="B9" t="n">
-        <v>79956</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520729</v>
+        <v>520475</v>
       </c>
       <c r="R9" t="n">
-        <v>6848525</v>
+        <v>6848386</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,48 +1456,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134263798</v>
+        <v>134273452</v>
       </c>
       <c r="B10" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+          <t>Öster om Los, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520420</v>
+        <v>520856</v>
       </c>
       <c r="R10" t="n">
-        <v>6848482</v>
+        <v>6848595</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1547,9 +1524,19 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1564,26 +1551,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134262435</v>
+        <v>134273461</v>
       </c>
       <c r="B11" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1607,17 +1594,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+          <t>Öster om Los, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520749</v>
+        <v>520769</v>
       </c>
       <c r="R11" t="n">
-        <v>6848568</v>
+        <v>6848593</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1644,9 +1631,19 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1661,60 +1658,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134262337</v>
+        <v>134273462</v>
       </c>
       <c r="B12" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+          <t>Öster om Los, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520727</v>
+        <v>520754</v>
       </c>
       <c r="R12" t="n">
-        <v>6848525</v>
+        <v>6848603</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1741,9 +1738,19 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1758,26 +1765,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134263717</v>
+        <v>134273463</v>
       </c>
       <c r="B13" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1801,17 +1808,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+          <t>Öster om Los, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520420</v>
+        <v>520749</v>
       </c>
       <c r="R13" t="n">
-        <v>6848523</v>
+        <v>6848588</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1838,9 +1845,19 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1855,60 +1872,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134263986</v>
+        <v>134273464</v>
       </c>
       <c r="B14" t="n">
-        <v>5201</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+          <t>Öster om Los, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520432</v>
+        <v>520753</v>
       </c>
       <c r="R14" t="n">
-        <v>6848456</v>
+        <v>6848581</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1935,14 +1952,19 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnaggångar</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1957,26 +1979,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134262818</v>
+        <v>134273480</v>
       </c>
       <c r="B15" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2000,17 +2022,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+          <t>Öster om Los, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520762</v>
+        <v>520593</v>
       </c>
       <c r="R15" t="n">
-        <v>6848627</v>
+        <v>6848428</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2037,9 +2059,19 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2054,57 +2086,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134263810</v>
+        <v>134273482</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+          <t>Öster om Los, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520420</v>
+        <v>520519</v>
       </c>
       <c r="R16" t="n">
-        <v>6848482</v>
+        <v>6848489</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2134,9 +2166,19 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2151,26 +2193,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134263036</v>
+        <v>134273484</v>
       </c>
       <c r="B17" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2194,17 +2236,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+          <t>Öster om Los, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520606</v>
+        <v>520484</v>
       </c>
       <c r="R17" t="n">
-        <v>6848503</v>
+        <v>6848493</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2231,9 +2273,19 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2248,60 +2300,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134263519</v>
+        <v>134273485</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+          <t>Öster om Los, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520595</v>
+        <v>520469</v>
       </c>
       <c r="R18" t="n">
-        <v>6848484</v>
+        <v>6848486</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2328,9 +2380,19 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2345,26 +2407,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134262683</v>
+        <v>134273492</v>
       </c>
       <c r="B19" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2388,17 +2450,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+          <t>Öster om Los, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520808</v>
+        <v>520414</v>
       </c>
       <c r="R19" t="n">
-        <v>6848642</v>
+        <v>6848451</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2425,14 +2487,19 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2447,44 +2514,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134263840</v>
+        <v>134262144</v>
       </c>
       <c r="B20" t="n">
-        <v>79366</v>
+        <v>79397</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2494,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520423</v>
+        <v>520672</v>
       </c>
       <c r="R20" t="n">
-        <v>6848466</v>
+        <v>6848461</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2544,44 +2611,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134262469</v>
+        <v>134263675</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79397</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2591,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520755</v>
+        <v>520443</v>
       </c>
       <c r="R21" t="n">
-        <v>6848585</v>
+        <v>6848531</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2653,48 +2720,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134262651</v>
+        <v>134290713</v>
       </c>
       <c r="B22" t="n">
-        <v>79985</v>
+        <v>79397</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+          <t>Slåttkölsmyrorna, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520810</v>
+        <v>520694</v>
       </c>
       <c r="R22" t="n">
-        <v>6848617</v>
+        <v>6848504</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2750,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134263477</v>
+        <v>118676090</v>
       </c>
       <c r="B23" t="n">
-        <v>79123</v>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2778,17 +2845,21 @@
           <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+          <t>Lillskog, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520595</v>
+        <v>520598</v>
       </c>
       <c r="R23" t="n">
-        <v>6848481</v>
+        <v>6848474</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2815,12 +2886,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2835,22 +2911,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134273484</v>
+        <v>134263477</v>
       </c>
       <c r="B24" t="n">
-        <v>79366</v>
+        <v>79130</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2858,37 +2934,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Öster om Los, Hls</t>
+          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520484</v>
+        <v>520595</v>
       </c>
       <c r="R24" t="n">
-        <v>6848493</v>
+        <v>6848481</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2915,19 +2991,9 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>16:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2942,22 +3008,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134273463</v>
+        <v>134263798</v>
       </c>
       <c r="B25" t="n">
-        <v>79366</v>
+        <v>79130</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2965,37 +3031,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Öster om Los, Hls</t>
+          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520749</v>
+        <v>520420</v>
       </c>
       <c r="R25" t="n">
-        <v>6848588</v>
+        <v>6848482</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3022,19 +3088,9 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>16:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3049,22 +3105,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134273485</v>
+        <v>134273437</v>
       </c>
       <c r="B26" t="n">
-        <v>79366</v>
+        <v>79130</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3072,21 +3128,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3096,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520469</v>
+        <v>520736</v>
       </c>
       <c r="R26" t="n">
-        <v>6848486</v>
+        <v>6848493</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3131,7 +3187,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3141,7 +3197,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3168,10 +3224,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134273492</v>
+        <v>134262208</v>
       </c>
       <c r="B27" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3179,37 +3235,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Öster om Los, Hls</t>
+          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520414</v>
+        <v>520658</v>
       </c>
       <c r="R27" t="n">
-        <v>6848451</v>
+        <v>6848461</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3236,19 +3292,9 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>17:08</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>17:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3275,10 +3321,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134273437</v>
+        <v>134262337</v>
       </c>
       <c r="B28" t="n">
-        <v>79123</v>
+        <v>79992</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3286,37 +3332,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Öster om Los, Hls</t>
+          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520736</v>
+        <v>520727</v>
       </c>
       <c r="R28" t="n">
-        <v>6848493</v>
+        <v>6848525</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3343,19 +3389,9 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:47</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:47</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3370,22 +3406,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134273464</v>
+        <v>134262651</v>
       </c>
       <c r="B29" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3393,37 +3429,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Öster om Los, Hls</t>
+          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520753</v>
+        <v>520810</v>
       </c>
       <c r="R29" t="n">
-        <v>6848581</v>
+        <v>6848617</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3450,19 +3486,9 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>16:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3477,22 +3503,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134273462</v>
+        <v>134263792</v>
       </c>
       <c r="B30" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3500,37 +3526,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Öster om Los, Hls</t>
+          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520754</v>
+        <v>520420</v>
       </c>
       <c r="R30" t="n">
-        <v>6848603</v>
+        <v>6848482</v>
       </c>
       <c r="S30" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3557,19 +3583,9 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>16:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3584,60 +3600,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134273461</v>
+        <v>134263986</v>
       </c>
       <c r="B31" t="n">
-        <v>79366</v>
+        <v>5201</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Öster om Los, Hls</t>
+          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520769</v>
+        <v>520432</v>
       </c>
       <c r="R31" t="n">
-        <v>6848593</v>
+        <v>6848456</v>
       </c>
       <c r="S31" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3664,19 +3680,14 @@
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>16:22</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3691,44 +3702,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134273452</v>
+        <v>134273496</v>
       </c>
       <c r="B32" t="n">
-        <v>79366</v>
+        <v>99195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3738,10 +3749,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520856</v>
+        <v>520386</v>
       </c>
       <c r="R32" t="n">
-        <v>6848595</v>
+        <v>6848452</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3773,7 +3784,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3783,7 +3794,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>+100</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3810,32 +3826,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134273496</v>
+        <v>134273479</v>
       </c>
       <c r="B33" t="n">
-        <v>99188</v>
+        <v>103907</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>223284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3845,10 +3861,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520386</v>
+        <v>520614</v>
       </c>
       <c r="R33" t="n">
-        <v>6848452</v>
+        <v>6848439</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3880,7 +3896,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3890,12 +3906,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>+100</t>
+          <t>Äldre sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3922,32 +3938,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134273480</v>
+        <v>134273494</v>
       </c>
       <c r="B34" t="n">
-        <v>79366</v>
+        <v>103907</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>223284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3957,10 +3973,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520593</v>
+        <v>520399</v>
       </c>
       <c r="R34" t="n">
-        <v>6848428</v>
+        <v>6848438</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3992,7 +4008,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4002,7 +4018,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre sälg med tickor.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4029,32 +4050,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134273482</v>
+        <v>134273495</v>
       </c>
       <c r="B35" t="n">
-        <v>79366</v>
+        <v>103907</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>223284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4064,13 +4085,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520519</v>
+        <v>520389</v>
       </c>
       <c r="R35" t="n">
-        <v>6848489</v>
+        <v>6848450</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4099,7 +4120,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4109,7 +4130,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre sälg med tickor och bohål.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4133,6 +4159,1199 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134273498</v>
+      </c>
+      <c r="B36" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Öster om Los, Hls</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>520407</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6848423</v>
+      </c>
+      <c r="S36" t="n">
+        <v>35</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134273499</v>
+      </c>
+      <c r="B37" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Öster om Los, Hls</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>520435</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6848391</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>118676089</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lillskog, Hls</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>520598</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6848474</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134262222</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>520664</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6848482</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134262469</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>520755</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6848585</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134262850</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>520753</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6848624</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>134263519</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>520595</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6848484</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134263810</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>520420</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6848482</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134290714</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Slåttkölsmyrorna, Hls</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>520694</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6848504</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134262137</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>520665</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6848450</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>134262331</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Slåttkölsmyran, Slåttkölsmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>520729</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6848525</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>134290712</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Slåttkölsmyrorna, Hls</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>520694</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6848504</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18986-2024 artfynd.xlsx
+++ b/artfynd/A 18986-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134262435</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134262683</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134262818</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134263036</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134263717</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134263840</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134264098</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134264254</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1560,6 +1605,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273452</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1667,6 +1717,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273461</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1774,6 +1829,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273462</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1881,6 +1941,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273463</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1988,6 +2053,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273464</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2095,6 +2165,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273480</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2202,6 +2277,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273482</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2309,6 +2389,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273484</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2416,6 +2501,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273485</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2523,6 +2613,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273492</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2620,6 +2715,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134262144</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2717,6 +2817,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134263675</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2814,6 +2919,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134290713</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2920,6 +3030,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118676090</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3017,6 +3132,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134263477</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3114,6 +3234,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134263798</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3221,6 +3346,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273437</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3318,6 +3448,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134262208</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3415,6 +3550,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134262337</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3512,6 +3652,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134262651</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3609,6 +3754,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134263792</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3711,6 +3861,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134263986</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3823,6 +3978,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273496</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3935,6 +4095,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273479</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4047,6 +4212,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273494</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4159,6 +4329,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273495</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4266,6 +4441,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273498</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4373,6 +4553,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134273499</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4479,6 +4664,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118676089</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4576,6 +4766,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134262222</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4673,6 +4868,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134262469</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4770,6 +4970,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134262850</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4867,6 +5072,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134263519</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4964,6 +5174,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134263810</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5061,6 +5276,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134290714</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5158,6 +5378,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134262137</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5255,6 +5480,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134262331</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5352,8 +5582,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134290712</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>